--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104022818</v>
+        <v>56357323</v>
       </c>
       <c r="B2" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Över-stormyran, Jmt</t>
+          <t>Storön, nordost om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570900.2992508583</v>
+        <v>570647</v>
       </c>
       <c r="R2" t="n">
-        <v>7011033.490143093</v>
+        <v>7011043</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2015-09-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,35 +756,43 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>gammal, olikåldrig granskog på fuktig mark</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga efter 190-årig gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110732662</v>
+        <v>104022848</v>
       </c>
       <c r="B3" t="n">
-        <v>78612</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Över-stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570787.1546896491</v>
+        <v>570989</v>
       </c>
       <c r="R3" t="n">
-        <v>7010961.085243583</v>
+        <v>7011121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,65 +884,68 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110732870</v>
+        <v>128800732</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Sörbyn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570747.9696998768</v>
+        <v>570788</v>
       </c>
       <c r="R4" t="n">
-        <v>7010976.465045825</v>
+        <v>7011017</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,62 +999,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110732668</v>
+        <v>103810533</v>
       </c>
       <c r="B5" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Fyrprickmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570725.2564141639</v>
+        <v>570896</v>
       </c>
       <c r="R5" t="n">
-        <v>7011044.081881361</v>
+        <v>7011023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,22 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,62 +1096,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110732669</v>
+        <v>104022818</v>
       </c>
       <c r="B6" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Över-stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570725.2564141639</v>
+        <v>570900</v>
       </c>
       <c r="R6" t="n">
-        <v>7011044.081881361</v>
+        <v>7011033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,22 +1173,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,49 +1203,48 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110732663</v>
+        <v>110732669</v>
       </c>
       <c r="B7" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570787.1546896491</v>
+        <v>570725</v>
       </c>
       <c r="R7" t="n">
-        <v>7010961.085243583</v>
+        <v>7011044</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,19 +1287,9 @@
           <t>2023-07-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,50 +1316,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110732661</v>
+        <v>104022822</v>
       </c>
       <c r="B8" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Över-stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570876.2088568852</v>
+        <v>570907</v>
       </c>
       <c r="R8" t="n">
-        <v>7011101.976752994</v>
+        <v>7011013</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,22 +1381,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,49 +1411,48 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110732660</v>
+        <v>110732668</v>
       </c>
       <c r="B9" t="n">
-        <v>96957</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222302</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570876.2088568852</v>
+        <v>570725</v>
       </c>
       <c r="R9" t="n">
-        <v>7011101.976752994</v>
+        <v>7011044</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,19 +1495,9 @@
           <t>2023-07-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,15 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110732872</v>
+        <v>110656423</v>
       </c>
       <c r="B10" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,14 +1555,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Fyrpickmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570747.9696998768</v>
+        <v>570686</v>
       </c>
       <c r="R10" t="n">
-        <v>7010976.465045825</v>
+        <v>7010977</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,22 +1589,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,6 +1618,1018 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110732663</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>570787</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7010961</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110732872</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>570748</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7010976</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128800730</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sörbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>571041</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7011148</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128800733</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sörbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>570787</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7011030</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110732870</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>570748</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7010976</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>110732662</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>570787</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7010961</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>110732661</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>570876</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7011102</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110656426</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>570686</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7010977</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>110732660</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99771</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222302</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spädstarr</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carex disperma</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>570876</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7011102</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104022834</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Över-stormyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>570906</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7011010</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357323</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104022848</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128800732</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103810533</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104022818</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732669</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104022822</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,6 +1561,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732668</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1618,6 +1663,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110656423</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1715,6 +1765,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732663</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1812,6 +1867,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732872</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1923,6 +1983,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128800730</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2034,6 +2099,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128800733</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2131,6 +2201,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732870</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2228,6 +2303,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732662</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2325,6 +2405,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732661</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110656426</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2519,6 +2609,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732660</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2630,8 +2725,34 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104022834</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104022848</v>
+        <v>135641262</v>
       </c>
       <c r="B3" t="n">
-        <v>97231</v>
+        <v>96454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,34 +810,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Över-stormyran, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570989</v>
+        <v>570846</v>
       </c>
       <c r="R3" t="n">
-        <v>7011121</v>
+        <v>7011001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,22 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,73 +884,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104022848</t>
+          <t>https://artportalen.se/Sighting/135641262</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128800732</v>
+        <v>104022848</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörbyn, Jmt</t>
+          <t>Över-stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570788</v>
+        <v>570989</v>
       </c>
       <c r="R4" t="n">
-        <v>7011017</v>
+        <v>7011121</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +966,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,65 +996,73 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128800732</t>
+          <t>https://artportalen.se/Sighting/104022848</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103810533</v>
+        <v>128800732</v>
       </c>
       <c r="B5" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fyrprickmyran, Jmt</t>
+          <t>Sörbyn, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570896</v>
+        <v>570788</v>
       </c>
       <c r="R5" t="n">
-        <v>7011023</v>
+        <v>7011017</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,12 +1086,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,62 +1116,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103810533</t>
+          <t>https://artportalen.se/Sighting/128800732</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104022818</v>
+        <v>135641257</v>
       </c>
       <c r="B6" t="n">
-        <v>93201</v>
+        <v>93313</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Över-stormyran, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570900</v>
+        <v>570808</v>
       </c>
       <c r="R6" t="n">
-        <v>7011033</v>
+        <v>7010931</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,22 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,31 +1218,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104022818</t>
+          <t>https://artportalen.se/Sighting/135641257</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110732669</v>
+        <v>103810533</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>93201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,34 +1246,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Fyrprickmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570725</v>
+        <v>570896</v>
       </c>
       <c r="R7" t="n">
-        <v>7011044</v>
+        <v>7011023</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,12 +1300,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,49 +1320,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732669</t>
+          <t>https://artportalen.se/Sighting/103810533</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104022822</v>
+        <v>104022818</v>
       </c>
       <c r="B8" t="n">
-        <v>78730</v>
+        <v>93201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570907</v>
+        <v>570900</v>
       </c>
       <c r="R8" t="n">
-        <v>7011013</v>
+        <v>7011033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,38 +1447,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104022822</t>
+          <t>https://artportalen.se/Sighting/104022818</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110732668</v>
+        <v>110732669</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1563,51 +1549,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732668</t>
+          <t>https://artportalen.se/Sighting/110732669</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110656423</v>
+        <v>135641263</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fyrpickmyran, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570686</v>
+        <v>570846</v>
       </c>
       <c r="R10" t="n">
-        <v>7010977</v>
+        <v>7010998</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,12 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,31 +1636,46 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110656423</t>
+          <t>https://artportalen.se/Sighting/135641263</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110732663</v>
+        <v>104022822</v>
       </c>
       <c r="B11" t="n">
-        <v>80432</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,34 +1683,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Över-stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570787</v>
+        <v>570907</v>
       </c>
       <c r="R11" t="n">
-        <v>7010961</v>
+        <v>7011013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,12 +1737,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,27 +1767,31 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732663</t>
+          <t>https://artportalen.se/Sighting/104022822</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110732872</v>
+        <v>135641261</v>
       </c>
       <c r="B12" t="n">
-        <v>80432</v>
+        <v>83398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,34 +1799,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570748</v>
+        <v>570790</v>
       </c>
       <c r="R12" t="n">
-        <v>7010976</v>
+        <v>7010969</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,12 +1853,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,31 +1869,46 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732872</t>
+          <t>https://artportalen.se/Sighting/135641261</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128800730</v>
+        <v>135641264</v>
       </c>
       <c r="B13" t="n">
-        <v>80432</v>
+        <v>83398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,38 +1916,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sörbyn, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571041</v>
+        <v>570845</v>
       </c>
       <c r="R13" t="n">
-        <v>7011148</v>
+        <v>7010998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,22 +1970,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,31 +1986,46 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128800730</t>
+          <t>https://artportalen.se/Sighting/135641264</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128800733</v>
+        <v>110732668</v>
       </c>
       <c r="B14" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,38 +2033,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sörbyn, Jmt</t>
+          <t>Gräslandbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570787</v>
+        <v>570725</v>
       </c>
       <c r="R14" t="n">
-        <v>7011030</v>
+        <v>7011044</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,22 +2087,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,62 +2107,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128800733</t>
+          <t>https://artportalen.se/Sighting/110732668</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110732870</v>
+        <v>135641260</v>
       </c>
       <c r="B15" t="n">
-        <v>80460</v>
+        <v>79497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570748</v>
+        <v>570796</v>
       </c>
       <c r="R15" t="n">
-        <v>7010976</v>
+        <v>7010953</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,12 +2189,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,62 +2209,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732870</t>
+          <t>https://artportalen.se/Sighting/135641260</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110732662</v>
+        <v>110656423</v>
       </c>
       <c r="B16" t="n">
-        <v>80468</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Fyrpickmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570787</v>
+        <v>570686</v>
       </c>
       <c r="R16" t="n">
-        <v>7010961</v>
+        <v>7010977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,12 +2291,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,38 +2322,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732662</t>
+          <t>https://artportalen.se/Sighting/110656423</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110732661</v>
+        <v>110732663</v>
       </c>
       <c r="B17" t="n">
-        <v>99022</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570876</v>
+        <v>570787</v>
       </c>
       <c r="R17" t="n">
-        <v>7011102</v>
+        <v>7010961</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,51 +2424,51 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732661</t>
+          <t>https://artportalen.se/Sighting/110732663</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110656426</v>
+        <v>110732872</v>
       </c>
       <c r="B18" t="n">
-        <v>99140</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fyrpickmyran, Jmt</t>
+          <t>Gräslandbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570686</v>
+        <v>570748</v>
       </c>
       <c r="R18" t="n">
-        <v>7010977</v>
+        <v>7010976</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,12 +2495,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,51 +2526,55 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110656426</t>
+          <t>https://artportalen.se/Sighting/110732872</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110732660</v>
+        <v>128800730</v>
       </c>
       <c r="B19" t="n">
-        <v>99771</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222302</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Dewey</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Sörbyn, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570876</v>
+        <v>571041</v>
       </c>
       <c r="R19" t="n">
-        <v>7011102</v>
+        <v>7011148</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,12 +2601,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2600,27 +2631,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732660</t>
+          <t>https://artportalen.se/Sighting/128800730</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104022834</v>
+        <v>128800733</v>
       </c>
       <c r="B20" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,34 +2659,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Över-stormyran, Jmt</t>
+          <t>Sörbyn, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570906</v>
+        <v>570787</v>
       </c>
       <c r="R20" t="n">
-        <v>7011010</v>
+        <v>7011030</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,22 +2717,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,20 +2747,1167 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128800733</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135641259</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80526</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>570790</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7010960</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641259</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>110732870</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>570748</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7010976</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732870</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>110732662</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>570787</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7010961</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732662</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>110732661</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>570876</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7011102</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732661</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135641266</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>570813</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7010952</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641266</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135641267</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>570805</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7010950</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641267</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>110656426</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>570686</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7010977</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110656426</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135641258</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99264</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>570798</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7010958</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641258</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>110732660</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99771</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222302</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spädstarr</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carex disperma</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>570876</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7011102</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732660</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135641265</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99048</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>570844</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7010987</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641265</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>104022834</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Över-stormyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>570906</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7011010</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Via Johan Staaf</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
+      <c r="AY31" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104022834</t>
         </is>
@@ -2752,6 +3934,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135641262</v>
       </c>
       <c r="B3" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135641257</v>
       </c>
       <c r="B6" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>135641263</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135641261</v>
       </c>
       <c r="B12" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>135641264</v>
       </c>
       <c r="B13" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>135641260</v>
       </c>
       <c r="B15" t="n">
-        <v>79497</v>
+        <v>79524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>135641259</v>
       </c>
       <c r="B21" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>135641266</v>
       </c>
       <c r="B25" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>135641267</v>
       </c>
       <c r="B26" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>135641258</v>
       </c>
       <c r="B28" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>135641265</v>
       </c>
       <c r="B30" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104022848</v>
+        <v>135641262</v>
       </c>
       <c r="B3" t="n">
-        <v>97231</v>
+        <v>96486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,34 +810,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Över-stormyran, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570989</v>
+        <v>570846</v>
       </c>
       <c r="R3" t="n">
-        <v>7011121</v>
+        <v>7011001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,22 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,73 +884,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104022848</t>
+          <t>https://artportalen.se/Sighting/135641262</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128800732</v>
+        <v>104022848</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörbyn, Jmt</t>
+          <t>Över-stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570788</v>
+        <v>570989</v>
       </c>
       <c r="R4" t="n">
-        <v>7011017</v>
+        <v>7011121</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +966,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,65 +996,73 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128800732</t>
+          <t>https://artportalen.se/Sighting/104022848</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103810533</v>
+        <v>128800732</v>
       </c>
       <c r="B5" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fyrprickmyran, Jmt</t>
+          <t>Sörbyn, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570896</v>
+        <v>570788</v>
       </c>
       <c r="R5" t="n">
-        <v>7011023</v>
+        <v>7011017</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,12 +1086,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,62 +1116,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103810533</t>
+          <t>https://artportalen.se/Sighting/128800732</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104022818</v>
+        <v>135641257</v>
       </c>
       <c r="B6" t="n">
-        <v>93201</v>
+        <v>93345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Över-stormyran, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570900</v>
+        <v>570808</v>
       </c>
       <c r="R6" t="n">
-        <v>7011033</v>
+        <v>7010931</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,22 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,31 +1218,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104022818</t>
+          <t>https://artportalen.se/Sighting/135641257</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110732669</v>
+        <v>103810533</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>93201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,34 +1246,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Fyrprickmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570725</v>
+        <v>570896</v>
       </c>
       <c r="R7" t="n">
-        <v>7011044</v>
+        <v>7011023</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,12 +1300,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,49 +1320,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732669</t>
+          <t>https://artportalen.se/Sighting/103810533</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104022822</v>
+        <v>104022818</v>
       </c>
       <c r="B8" t="n">
-        <v>78730</v>
+        <v>93201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570907</v>
+        <v>570900</v>
       </c>
       <c r="R8" t="n">
-        <v>7011013</v>
+        <v>7011033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,38 +1447,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104022822</t>
+          <t>https://artportalen.se/Sighting/104022818</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110732668</v>
+        <v>110732669</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1563,51 +1549,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732668</t>
+          <t>https://artportalen.se/Sighting/110732669</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110656423</v>
+        <v>135641263</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fyrpickmyran, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570686</v>
+        <v>570846</v>
       </c>
       <c r="R10" t="n">
-        <v>7010977</v>
+        <v>7010998</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,12 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,31 +1636,46 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110656423</t>
+          <t>https://artportalen.se/Sighting/135641263</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110732663</v>
+        <v>104022822</v>
       </c>
       <c r="B11" t="n">
-        <v>80432</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,34 +1683,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Över-stormyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570787</v>
+        <v>570907</v>
       </c>
       <c r="R11" t="n">
-        <v>7010961</v>
+        <v>7011013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,12 +1737,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,27 +1767,31 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732663</t>
+          <t>https://artportalen.se/Sighting/104022822</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110732872</v>
+        <v>135641261</v>
       </c>
       <c r="B12" t="n">
-        <v>80432</v>
+        <v>83428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,34 +1799,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570748</v>
+        <v>570790</v>
       </c>
       <c r="R12" t="n">
-        <v>7010976</v>
+        <v>7010969</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,12 +1853,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,31 +1869,46 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732872</t>
+          <t>https://artportalen.se/Sighting/135641261</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128800730</v>
+        <v>135641264</v>
       </c>
       <c r="B13" t="n">
-        <v>80432</v>
+        <v>83428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,38 +1916,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sörbyn, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571041</v>
+        <v>570845</v>
       </c>
       <c r="R13" t="n">
-        <v>7011148</v>
+        <v>7010998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,22 +1970,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:51</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,31 +1986,46 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128800730</t>
+          <t>https://artportalen.se/Sighting/135641264</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128800733</v>
+        <v>110732668</v>
       </c>
       <c r="B14" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,38 +2033,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sörbyn, Jmt</t>
+          <t>Gräslandbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570787</v>
+        <v>570725</v>
       </c>
       <c r="R14" t="n">
-        <v>7011030</v>
+        <v>7011044</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,22 +2087,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,62 +2107,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128800733</t>
+          <t>https://artportalen.se/Sighting/110732668</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110732870</v>
+        <v>135641260</v>
       </c>
       <c r="B15" t="n">
-        <v>80460</v>
+        <v>79527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570748</v>
+        <v>570796</v>
       </c>
       <c r="R15" t="n">
-        <v>7010976</v>
+        <v>7010953</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,12 +2189,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,62 +2209,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732870</t>
+          <t>https://artportalen.se/Sighting/135641260</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110732662</v>
+        <v>110656423</v>
       </c>
       <c r="B16" t="n">
-        <v>80468</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Fyrpickmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570787</v>
+        <v>570686</v>
       </c>
       <c r="R16" t="n">
-        <v>7010961</v>
+        <v>7010977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,12 +2291,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,38 +2322,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732662</t>
+          <t>https://artportalen.se/Sighting/110656423</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110732661</v>
+        <v>110732663</v>
       </c>
       <c r="B17" t="n">
-        <v>99022</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570876</v>
+        <v>570787</v>
       </c>
       <c r="R17" t="n">
-        <v>7011102</v>
+        <v>7010961</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,51 +2424,51 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732661</t>
+          <t>https://artportalen.se/Sighting/110732663</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110656426</v>
+        <v>110732872</v>
       </c>
       <c r="B18" t="n">
-        <v>99140</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fyrpickmyran, Jmt</t>
+          <t>Gräslandbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570686</v>
+        <v>570748</v>
       </c>
       <c r="R18" t="n">
-        <v>7010977</v>
+        <v>7010976</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,12 +2495,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,51 +2526,55 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110656426</t>
+          <t>https://artportalen.se/Sighting/110732872</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110732660</v>
+        <v>128800730</v>
       </c>
       <c r="B19" t="n">
-        <v>99771</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222302</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Dewey</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gräslandbäcken, Jmt</t>
+          <t>Sörbyn, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570876</v>
+        <v>571041</v>
       </c>
       <c r="R19" t="n">
-        <v>7011102</v>
+        <v>7011148</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,12 +2601,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2600,27 +2631,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110732660</t>
+          <t>https://artportalen.se/Sighting/128800730</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104022834</v>
+        <v>128800733</v>
       </c>
       <c r="B20" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,34 +2659,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Över-stormyran, Jmt</t>
+          <t>Sörbyn, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570906</v>
+        <v>570787</v>
       </c>
       <c r="R20" t="n">
-        <v>7011010</v>
+        <v>7011030</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,22 +2717,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,20 +2747,1167 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128800733</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135641259</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>570790</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7010960</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641259</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>110732870</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>570748</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7010976</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732870</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>110732662</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>570787</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7010961</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732662</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>110732661</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>570876</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7011102</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732661</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135641266</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>570813</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7010952</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641266</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135641267</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>570805</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7010950</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641267</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>110656426</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>570686</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7010977</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110656426</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135641258</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>570798</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7010958</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641258</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>110732660</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99771</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222302</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spädstarr</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carex disperma</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gräslandbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>570876</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7011102</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110732660</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135641265</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fyrpickmyran, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>570844</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7010987</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641265</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>104022834</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Över-stormyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>570906</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7011010</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Via Johan Staaf</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
+      <c r="AY31" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104022834</t>
         </is>
@@ -2752,6 +3934,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135641262</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135641257</v>
       </c>
       <c r="B6" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>135641266</v>
       </c>
       <c r="B25" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>135641267</v>
       </c>
       <c r="B26" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>135641258</v>
       </c>
       <c r="B28" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>135641265</v>
       </c>
       <c r="B30" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135641262</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135641257</v>
       </c>
       <c r="B6" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>135641263</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135641261</v>
       </c>
       <c r="B12" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>135641264</v>
       </c>
       <c r="B13" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>135641260</v>
       </c>
       <c r="B15" t="n">
-        <v>79527</v>
+        <v>79529</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>135641259</v>
       </c>
       <c r="B21" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>135641266</v>
       </c>
       <c r="B25" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>135641267</v>
       </c>
       <c r="B26" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>135641258</v>
       </c>
       <c r="B28" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>135641265</v>
       </c>
       <c r="B30" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135641262</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135641257</v>
       </c>
       <c r="B6" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>135641263</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135641261</v>
       </c>
       <c r="B12" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>135641264</v>
       </c>
       <c r="B13" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>135641260</v>
       </c>
       <c r="B15" t="n">
-        <v>79529</v>
+        <v>79530</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>135641259</v>
       </c>
       <c r="B21" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>135641266</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>135641267</v>
       </c>
       <c r="B26" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>135641258</v>
       </c>
       <c r="B28" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>135641265</v>
       </c>
       <c r="B30" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135641262</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135641257</v>
       </c>
       <c r="B6" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>135641266</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>135641267</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>135641258</v>
       </c>
       <c r="B28" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>135641265</v>
       </c>
       <c r="B30" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135641262</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135641257</v>
       </c>
       <c r="B6" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>135641263</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135641261</v>
       </c>
       <c r="B12" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>135641264</v>
       </c>
       <c r="B13" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>135641260</v>
       </c>
       <c r="B15" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>135641259</v>
       </c>
       <c r="B21" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>135641266</v>
       </c>
       <c r="B25" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>135641267</v>
       </c>
       <c r="B26" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>135641258</v>
       </c>
       <c r="B28" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>135641265</v>
       </c>
       <c r="B30" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 3634-2024 artfynd.xlsx
+++ b/artfynd/A 3634-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>135641262</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135641257</v>
       </c>
       <c r="B6" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>135641263</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>135641261</v>
       </c>
       <c r="B12" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>135641264</v>
       </c>
       <c r="B13" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>135641260</v>
       </c>
       <c r="B15" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>135641259</v>
       </c>
       <c r="B21" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>135641266</v>
       </c>
       <c r="B25" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>135641267</v>
       </c>
       <c r="B26" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>135641258</v>
       </c>
       <c r="B28" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>135641265</v>
       </c>
       <c r="B30" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
